--- a/tests/outputs/write_rows.xlsx
+++ b/tests/outputs/write_rows.xlsx
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,20 +53,8 @@
         <fgColor rgb="000066CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-        <bgColor rgb="00FF9999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0078FF66"/>
-        <bgColor rgb="0078FF66"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -80,36 +68,16 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00808080"/>
-      </left>
-      <right style="thin">
-        <color rgb="00808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="00808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -192,12 +160,11 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pytest</author>
-    <author/>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>offer_id</t>
+        <t>Offer</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
@@ -208,11 +175,6 @@
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>Very green</t>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="1" shapeId="0">
-      <text>
-        <t>Fixed</t>
       </text>
     </comment>
   </commentList>
@@ -552,7 +514,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>this has been fixed</t>
         </is>
@@ -569,18 +531,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>10</v>
       </c>
     </row>
